--- a/diseases/d058/2020-2025.xlsx
+++ b/diseases/d058/2020-2025.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>57</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.109914518033082</v>
       </c>
@@ -2393,9 +2390,6 @@
       <c r="O13" t="n">
         <v>29</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.05592142145542769</v>
       </c>
@@ -3577,9 +3571,6 @@
       <c r="O21" t="n">
         <v>24</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.04627979706656084</v>
       </c>
@@ -4761,9 +4752,6 @@
       <c r="O29" t="n">
         <v>43</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.08291796974425486</v>
       </c>
@@ -6093,9 +6081,6 @@
       <c r="O38" t="n">
         <v>72</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1388393911996825</v>
       </c>
@@ -7277,9 +7262,6 @@
       <c r="O46" t="n">
         <v>80</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1542659902218695</v>
       </c>
@@ -8461,9 +8443,6 @@
       <c r="O54" t="n">
         <v>80</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1542659902218695</v>
       </c>
@@ -9793,9 +9772,6 @@
       <c r="O63" t="n">
         <v>59</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.1137711677886288</v>
       </c>
@@ -10977,9 +10953,6 @@
       <c r="O71" t="n">
         <v>101</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.1947608126551102</v>
       </c>
@@ -12161,9 +12134,6 @@
       <c r="O79" t="n">
         <v>890</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>1.716209141218298</v>
       </c>
@@ -13493,9 +13463,6 @@
       <c r="O88" t="n">
         <v>2594</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>5.002074732944118</v>
       </c>
@@ -14677,9 +14644,6 @@
       <c r="O96" t="n">
         <v>450</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.8677461949980159</v>
       </c>
@@ -16009,9 +15973,6 @@
       <c r="O105" t="n">
         <v>67</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.1292228944973661</v>
       </c>
@@ -17193,9 +17154,6 @@
       <c r="O113" t="n">
         <v>44</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.08486279638632997</v>
       </c>
@@ -18377,9 +18335,6 @@
       <c r="O121" t="n">
         <v>49</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.09450629597568565</v>
       </c>
@@ -19561,9 +19516,6 @@
       <c r="O129" t="n">
         <v>68</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.1311515944152372</v>
       </c>
@@ -20893,9 +20845,6 @@
       <c r="O138" t="n">
         <v>97</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.1870838920335001</v>
       </c>
@@ -22077,9 +22026,6 @@
       <c r="O146" t="n">
         <v>108</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.2082995911300827</v>
       </c>
@@ -23261,9 +23207,6 @@
       <c r="O154" t="n">
         <v>105</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.2025134913764693</v>
       </c>
@@ -24593,9 +24536,6 @@
       <c r="O163" t="n">
         <v>101</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.1947986917049847</v>
       </c>
@@ -25777,9 +25717,6 @@
       <c r="O171" t="n">
         <v>94</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1812977922798868</v>
       </c>
@@ -27109,9 +27046,6 @@
       <c r="O180" t="n">
         <v>1219</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.351085199884914</v>
       </c>
@@ -28293,9 +28227,6 @@
       <c r="O188" t="n">
         <v>3469</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>6.69066001509497</v>
       </c>
@@ -29477,9 +29408,6 @@
       <c r="O196" t="n">
         <v>494</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.9527777594283411</v>
       </c>
@@ -30809,9 +30737,6 @@
       <c r="O205" t="n">
         <v>104</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.2008400075380662</v>
       </c>
@@ -31993,9 +31918,6 @@
       <c r="O213" t="n">
         <v>45</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.08690192633858634</v>
       </c>
@@ -33177,9 +33099,6 @@
       <c r="O221" t="n">
         <v>33</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.06372807931496331</v>
       </c>
@@ -34509,9 +34428,6 @@
       <c r="O230" t="n">
         <v>67</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.1293873125485619</v>
       </c>
@@ -35693,9 +35609,6 @@
       <c r="O238" t="n">
         <v>94</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.1815284683517137</v>
       </c>
@@ -36877,9 +36790,6 @@
       <c r="O246" t="n">
         <v>130</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.2510500094225828</v>
       </c>
@@ -38209,9 +38119,6 @@
       <c r="O255" t="n">
         <v>121</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.2336696241548655</v>
       </c>
@@ -39393,9 +39300,6 @@
       <c r="O263" t="n">
         <v>123</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.237531931992136</v>
       </c>
@@ -40577,9 +40481,6 @@
       <c r="O271" t="n">
         <v>180</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.3476077053543454</v>
       </c>
@@ -41909,9 +41810,6 @@
       <c r="O280" t="n">
         <v>1547</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>2.987495112128735</v>
       </c>
@@ -43093,9 +42991,6 @@
       <c r="O288" t="n">
         <v>3423</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>6.610339863488468</v>
       </c>
@@ -44277,9 +44172,6 @@
       <c r="O296" t="n">
         <v>368</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.7106646420577727</v>
       </c>
@@ -45609,9 +45501,6 @@
       <c r="O305" t="n">
         <v>99</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0.1913090094813711</v>
       </c>
@@ -46793,9 +46682,6 @@
       <c r="O313" t="n">
         <v>58</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.1120800257567629</v>
       </c>
@@ -47829,9 +47715,6 @@
       <c r="O320" t="n">
         <v>70</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.1352689966029897</v>
       </c>
@@ -49161,9 +49044,6 @@
       <c r="O329" t="n">
         <v>97</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.187444181007</v>
       </c>
@@ -50345,9 +50225,6 @@
       <c r="O337" t="n">
         <v>118</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.2280248799878969</v>
       </c>
@@ -51529,9 +51406,6 @@
       <c r="O345" t="n">
         <v>151</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.2917945498150206</v>
       </c>
@@ -52861,9 +52735,6 @@
       <c r="O354" t="n">
         <v>98</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.1893765952441856</v>
       </c>
@@ -54045,9 +53916,6 @@
       <c r="O362" t="n">
         <v>133</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.2570110935456804</v>
       </c>
@@ -55377,9 +55245,6 @@
       <c r="O371" t="n">
         <v>131</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.2531462650713093</v>
       </c>
@@ -56561,9 +56426,6 @@
       <c r="O379" t="n">
         <v>925</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>1.78748316939665</v>
       </c>
@@ -57597,9 +57459,6 @@
       <c r="O386" t="n">
         <v>3323</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>6.421412510167639</v>
       </c>
@@ -58781,9 +58640,6 @@
       <c r="O394" t="n">
         <v>460</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.8889105491053608</v>
       </c>
@@ -59817,9 +59673,6 @@
       <c r="O401" t="n">
         <v>157</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.30357176349478</v>
       </c>
@@ -60853,9 +60706,6 @@
       <c r="O408" t="n">
         <v>75</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.145018358357379</v>
       </c>
@@ -62037,9 +61887,6 @@
       <c r="O416" t="n">
         <v>56</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.1082803742401763</v>
       </c>
@@ -63073,9 +62920,6 @@
       <c r="O423" t="n">
         <v>102</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0.1972249673660354</v>
       </c>
@@ -64109,9 +63953,6 @@
       <c r="O430" t="n">
         <v>137</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0.2649002012661456</v>
       </c>
@@ -65293,9 +65134,6 @@
       <c r="O438" t="n">
         <v>140</v>
       </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
       <c r="R438" t="n">
         <v>0.2707009356004408</v>
       </c>
@@ -66329,9 +66167,6 @@
       <c r="O445" t="n">
         <v>154</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0.2977710291604849</v>
       </c>
@@ -67365,9 +67200,6 @@
       <c r="O452" t="n">
         <v>142</v>
       </c>
-      <c r="Q452" t="n">
-        <v>0</v>
-      </c>
       <c r="R452" t="n">
         <v>0.2745680918233042</v>
       </c>
@@ -68549,9 +68381,6 @@
       <c r="O460" t="n">
         <v>59</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0.1140811085744715</v>
       </c>
@@ -69585,9 +69414,6 @@
       <c r="O467" t="n">
         <v>903</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>1.746021034622843</v>
       </c>
@@ -70769,9 +70595,6 @@
       <c r="O475" t="n">
         <v>3174</v>
       </c>
-      <c r="Q475" t="n">
-        <v>0</v>
-      </c>
       <c r="R475" t="n">
         <v>6.137176925684279</v>
       </c>
@@ -71805,9 +71628,6 @@
       <c r="O482" t="n">
         <v>1169</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>2.26035281226368</v>
       </c>
@@ -72841,9 +72661,6 @@
       <c r="O489" t="n">
         <v>19</v>
       </c>
-      <c r="Q489" t="n">
-        <v>0</v>
-      </c>
       <c r="R489" t="n">
         <v>0.03677393530046081</v>
       </c>
@@ -74025,9 +73842,6 @@
       <c r="O497" t="n">
         <v>5</v>
       </c>
-      <c r="Q497" t="n">
-        <v>0</v>
-      </c>
       <c r="R497" t="n">
         <v>0.009677351394858107</v>
       </c>
@@ -75061,9 +74875,6 @@
       <c r="O504" t="n">
         <v>8</v>
       </c>
-      <c r="Q504" t="n">
-        <v>0</v>
-      </c>
       <c r="R504" t="n">
         <v>0.01548376223177297</v>
       </c>
@@ -76097,9 +75908,6 @@
       <c r="O511" t="n">
         <v>23</v>
       </c>
-      <c r="Q511" t="n">
-        <v>0</v>
-      </c>
       <c r="R511" t="n">
         <v>0.0445158164163473</v>
       </c>
@@ -77133,9 +76941,6 @@
       <c r="O518" t="n">
         <v>45</v>
       </c>
-      <c r="Q518" t="n">
-        <v>0</v>
-      </c>
       <c r="R518" t="n">
         <v>0.08709616255372297</v>
       </c>
@@ -78317,9 +78122,6 @@
       <c r="O526" t="n">
         <v>44</v>
       </c>
-      <c r="Q526" t="n">
-        <v>0</v>
-      </c>
       <c r="R526" t="n">
         <v>0.08516069227475136</v>
       </c>
@@ -79353,9 +79155,6 @@
       <c r="O533" t="n">
         <v>28</v>
       </c>
-      <c r="Q533" t="n">
-        <v>0</v>
-      </c>
       <c r="R533" t="n">
         <v>0.05419316781120541</v>
       </c>
@@ -80537,9 +80336,6 @@
       <c r="O541" t="n">
         <v>26</v>
       </c>
-      <c r="Q541" t="n">
-        <v>0</v>
-      </c>
       <c r="R541" t="n">
         <v>0.05032222725326217</v>
       </c>
@@ -81573,9 +81369,6 @@
       <c r="O548" t="n">
         <v>33</v>
       </c>
-      <c r="Q548" t="n">
-        <v>0</v>
-      </c>
       <c r="R548" t="n">
         <v>0.06387051920606351</v>
       </c>
@@ -82609,9 +82402,6 @@
       <c r="O555" t="n">
         <v>442</v>
       </c>
-      <c r="Q555" t="n">
-        <v>0</v>
-      </c>
       <c r="R555" t="n">
         <v>0.8554778633054567</v>
       </c>
@@ -83793,9 +83583,6 @@
       <c r="O563" t="n">
         <v>2255</v>
       </c>
-      <c r="Q563" t="n">
-        <v>0</v>
-      </c>
       <c r="R563" t="n">
         <v>4.364485479081006</v>
       </c>
@@ -84828,9 +84615,6 @@
       </c>
       <c r="O570" t="n">
         <v>477</v>
-      </c>
-      <c r="Q570" t="n">
-        <v>0</v>
       </c>
       <c r="R570" t="n">
         <v>0.9232193230694634</v>
